--- a/02_Inputs/avatars/Avatars.xlsx
+++ b/02_Inputs/avatars/Avatars.xlsx
@@ -1,37 +1,125 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\fschiubuntu\home\fschi\undp\dsc-energy-academy-pipeline\02_Inputs\avatars\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17BE5AD2-8356-4D64-930F-D3566279DCB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-38510" yWindow="-2580" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
+  <si>
+    <t>Lesson</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Voice</t>
+  </si>
+  <si>
+    <t>Accent</t>
+  </si>
+  <si>
+    <t>Background</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Part</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>1.0.0</t>
+  </si>
+  <si>
+    <t>ar</t>
+  </si>
+  <si>
+    <t>Darnell in Blue Shirt (Front)</t>
+  </si>
+  <si>
+    <t>Shakir - Professional</t>
+  </si>
+  <si>
+    <t>Arabic (Egypt)</t>
+  </si>
+  <si>
+    <t>solarpark</t>
+  </si>
+  <si>
+    <t>generated</t>
+  </si>
+  <si>
+    <t>male</t>
+  </si>
+  <si>
+    <t>pending</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,94 +134,107 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2BCC6DE0-16C5-4B16-AE4A-EDADE26AD41E}" name="Table1" displayName="Table1" ref="A1:I1048576" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
+  <autoFilter ref="A1:I1048576" xr:uid="{2BCC6DE0-16C5-4B16-AE4A-EDADE26AD41E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:I743">
+    <sortCondition ref="E1:E1048576"/>
+  </sortState>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{FF615655-1955-45D0-BBD6-794D4DD61F89}" name="Lesson"/>
+    <tableColumn id="2" xr3:uid="{1995849F-29EC-4DAE-9377-6CBE46FC9E53}" name="Language"/>
+    <tableColumn id="3" xr3:uid="{06D05249-B406-4421-81EB-3F39105DF8DA}" name="Name"/>
+    <tableColumn id="4" xr3:uid="{EE7F6CD3-8CBD-419F-A14A-15A651AB6962}" name="Voice"/>
+    <tableColumn id="5" xr3:uid="{11888FD6-F349-4737-8F20-4E2E58FDF144}" name="Accent"/>
+    <tableColumn id="6" xr3:uid="{8F7C3F54-FCDB-4E5B-BE65-9E34A7F81D5F}" name="Background"/>
+    <tableColumn id="7" xr3:uid="{1B048A90-624A-447F-9A85-09EB04833433}" name="Status"/>
+    <tableColumn id="8" xr3:uid="{517CAC7F-8897-4E30-94C4-4808EDFE4AED}" name="Part"/>
+    <tableColumn id="9" xr3:uid="{8830CC2A-A7BF-49BA-B57E-A88209C6C7D8}" name="Gender"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -420,99 +521,1383 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I743"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="10.265625" customWidth="1"/>
+    <col min="3" max="3" width="46.59765625" customWidth="1"/>
+    <col min="4" max="4" width="43.1328125" customWidth="1"/>
+    <col min="5" max="5" width="41.59765625" customWidth="1"/>
+    <col min="6" max="6" width="55.1328125" customWidth="1"/>
+    <col min="7" max="7" width="54.1328125" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Lesson</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Language</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Gender</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Voice</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Accent</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Script</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1.0.-1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Abigail Office Front</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>William Axel</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Original</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>generated</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Welcome to the Sustainable Energy Academy!I will be your guide throughout this journey. Together, we’ll explore how energy powers progress, shapes policy, and transforms lives.In this first module, you’ll learn why energy is far more than infrastructure — it’s the engine of sustainable development, climate resilience, and social justice.We’ll explore the critical role of energy in achieving the Sustainable Development Goals, especially SDG 7: ensuring access to affordable, reliable, sustainable, and modern energy for all. Currently, nearly 1.18 billion people live in energy poverty — a challenge this Academy is designed to help address.You’ll also see how UNDP’s “Energy Moonshot” aims to support 500 million people in accessing clean energy by 2025, and how diverse sectors — from finance and health to governance and gender — are all connected through energy.Let’s begin this learning journey together.</t>
-        </is>
-      </c>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="38" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+    </row>
+    <row r="39" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+    </row>
+    <row r="46" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+    </row>
+    <row r="47" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+    </row>
+    <row r="50" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+    </row>
+    <row r="51" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+    </row>
+    <row r="54" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+    </row>
+    <row r="55" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+    </row>
+    <row r="56" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+    </row>
+    <row r="57" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+    </row>
+    <row r="70" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+    </row>
+    <row r="71" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+    </row>
+    <row r="84" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+    </row>
+    <row r="85" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+    </row>
+    <row r="88" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+    </row>
+    <row r="89" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+    </row>
+    <row r="90" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+    </row>
+    <row r="91" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+    </row>
+    <row r="98" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+    </row>
+    <row r="99" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+    </row>
+    <row r="110" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
+    </row>
+    <row r="111" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C111" s="2"/>
+      <c r="D111" s="2"/>
+    </row>
+    <row r="122" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
+    </row>
+    <row r="123" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C123" s="2"/>
+      <c r="D123" s="2"/>
+    </row>
+    <row r="130" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
+    </row>
+    <row r="131" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C131" s="2"/>
+      <c r="D131" s="2"/>
+    </row>
+    <row r="134" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C134" s="2"/>
+      <c r="D134" s="2"/>
+    </row>
+    <row r="135" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C135" s="2"/>
+      <c r="D135" s="2"/>
+    </row>
+    <row r="142" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C142" s="2"/>
+      <c r="D142" s="2"/>
+    </row>
+    <row r="143" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C143" s="2"/>
+      <c r="D143" s="2"/>
+    </row>
+    <row r="152" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C152" s="2"/>
+      <c r="D152" s="2"/>
+      <c r="E152" s="2"/>
+    </row>
+    <row r="153" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
+      <c r="E153" s="2"/>
+    </row>
+    <row r="154" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
+      <c r="E154" s="2"/>
+    </row>
+    <row r="155" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C155" s="2"/>
+      <c r="D155" s="2"/>
+      <c r="E155" s="2"/>
+    </row>
+    <row r="166" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C166" s="2"/>
+      <c r="D166" s="2"/>
+      <c r="E166" s="2"/>
+    </row>
+    <row r="167" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C167" s="2"/>
+      <c r="D167" s="2"/>
+      <c r="E167" s="2"/>
+    </row>
+    <row r="168" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C168" s="2"/>
+      <c r="D168" s="2"/>
+      <c r="E168" s="2"/>
+    </row>
+    <row r="169" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C169" s="2"/>
+      <c r="D169" s="2"/>
+      <c r="E169" s="2"/>
+    </row>
+    <row r="178" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C178" s="2"/>
+      <c r="D178" s="2"/>
+      <c r="E178" s="2"/>
+    </row>
+    <row r="179" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C179" s="2"/>
+      <c r="D179" s="2"/>
+      <c r="E179" s="2"/>
+    </row>
+    <row r="180" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C180" s="2"/>
+      <c r="D180" s="2"/>
+      <c r="E180" s="2"/>
+    </row>
+    <row r="181" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C181" s="2"/>
+      <c r="D181" s="2"/>
+      <c r="E181" s="2"/>
+    </row>
+    <row r="192" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C192" s="2"/>
+      <c r="D192" s="2"/>
+      <c r="E192" s="2"/>
+    </row>
+    <row r="193" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C193" s="2"/>
+      <c r="D193" s="2"/>
+      <c r="E193" s="2"/>
+    </row>
+    <row r="198" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C198" s="2"/>
+      <c r="D198" s="2"/>
+      <c r="E198" s="2"/>
+    </row>
+    <row r="199" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C199" s="2"/>
+      <c r="D199" s="2"/>
+      <c r="E199" s="2"/>
+    </row>
+    <row r="200" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C200" s="2"/>
+      <c r="D200" s="2"/>
+      <c r="E200" s="2"/>
+    </row>
+    <row r="201" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C201" s="2"/>
+      <c r="D201" s="2"/>
+      <c r="E201" s="2"/>
+    </row>
+    <row r="218" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C218" s="2"/>
+      <c r="D218" s="2"/>
+      <c r="E218" s="2"/>
+    </row>
+    <row r="219" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C219" s="2"/>
+      <c r="D219" s="2"/>
+      <c r="E219" s="2"/>
+    </row>
+    <row r="224" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C224" s="2"/>
+      <c r="D224" s="2"/>
+      <c r="E224" s="2"/>
+    </row>
+    <row r="225" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C225" s="2"/>
+      <c r="D225" s="2"/>
+      <c r="E225" s="2"/>
+    </row>
+    <row r="234" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C234" s="2"/>
+      <c r="D234" s="2"/>
+      <c r="E234" s="2"/>
+    </row>
+    <row r="235" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C235" s="2"/>
+      <c r="D235" s="2"/>
+      <c r="E235" s="2"/>
+    </row>
+    <row r="240" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C240" s="2"/>
+      <c r="D240" s="2"/>
+      <c r="E240" s="2"/>
+    </row>
+    <row r="241" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C241" s="2"/>
+      <c r="D241" s="2"/>
+      <c r="E241" s="2"/>
+    </row>
+    <row r="252" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C252" s="2"/>
+      <c r="D252" s="2"/>
+      <c r="E252" s="2"/>
+    </row>
+    <row r="253" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C253" s="2"/>
+      <c r="D253" s="2"/>
+      <c r="E253" s="2"/>
+    </row>
+    <row r="260" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C260" s="2"/>
+      <c r="D260" s="2"/>
+      <c r="E260" s="2"/>
+    </row>
+    <row r="261" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C261" s="2"/>
+      <c r="D261" s="2"/>
+      <c r="E261" s="2"/>
+    </row>
+    <row r="262" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C262" s="2"/>
+      <c r="D262" s="2"/>
+      <c r="E262" s="2"/>
+    </row>
+    <row r="263" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C263" s="2"/>
+      <c r="D263" s="2"/>
+      <c r="E263" s="2"/>
+    </row>
+    <row r="266" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C266" s="2"/>
+      <c r="D266" s="2"/>
+      <c r="E266" s="2"/>
+    </row>
+    <row r="267" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C267" s="2"/>
+      <c r="D267" s="2"/>
+      <c r="E267" s="2"/>
+    </row>
+    <row r="280" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C280" s="2"/>
+      <c r="D280" s="2"/>
+      <c r="E280" s="2"/>
+    </row>
+    <row r="281" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C281" s="2"/>
+      <c r="D281" s="2"/>
+      <c r="E281" s="2"/>
+    </row>
+    <row r="286" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C286" s="2"/>
+      <c r="D286" s="2"/>
+      <c r="E286" s="2"/>
+    </row>
+    <row r="287" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C287" s="2"/>
+      <c r="D287" s="2"/>
+      <c r="E287" s="2"/>
+    </row>
+    <row r="288" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C288" s="2"/>
+      <c r="D288" s="2"/>
+      <c r="E288" s="2"/>
+    </row>
+    <row r="289" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C289" s="2"/>
+      <c r="D289" s="2"/>
+      <c r="E289" s="2"/>
+    </row>
+    <row r="300" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C300" s="2"/>
+      <c r="D300" s="2"/>
+      <c r="E300" s="2"/>
+    </row>
+    <row r="301" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C301" s="2"/>
+      <c r="D301" s="2"/>
+      <c r="E301" s="2"/>
+    </row>
+    <row r="302" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C302" s="2"/>
+      <c r="D302" s="2"/>
+      <c r="E302" s="2"/>
+    </row>
+    <row r="303" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C303" s="2"/>
+      <c r="D303" s="2"/>
+      <c r="E303" s="2"/>
+    </row>
+    <row r="314" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C314" s="2"/>
+      <c r="D314" s="2"/>
+      <c r="E314" s="2"/>
+    </row>
+    <row r="315" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C315" s="2"/>
+      <c r="D315" s="2"/>
+      <c r="E315" s="2"/>
+    </row>
+    <row r="316" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C316" s="2"/>
+      <c r="D316" s="2"/>
+      <c r="E316" s="2"/>
+    </row>
+    <row r="317" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C317" s="2"/>
+      <c r="D317" s="2"/>
+      <c r="E317" s="2"/>
+    </row>
+    <row r="328" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C328" s="2"/>
+      <c r="D328" s="2"/>
+      <c r="E328" s="2"/>
+    </row>
+    <row r="329" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C329" s="2"/>
+      <c r="D329" s="2"/>
+      <c r="E329" s="2"/>
+    </row>
+    <row r="330" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C330" s="2"/>
+      <c r="D330" s="2"/>
+      <c r="E330" s="2"/>
+    </row>
+    <row r="331" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C331" s="2"/>
+      <c r="D331" s="2"/>
+      <c r="E331" s="2"/>
+    </row>
+    <row r="342" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C342" s="2"/>
+      <c r="D342" s="2"/>
+      <c r="E342" s="2"/>
+    </row>
+    <row r="343" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C343" s="2"/>
+      <c r="D343" s="2"/>
+      <c r="E343" s="2"/>
+    </row>
+    <row r="350" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C350" s="2"/>
+      <c r="D350" s="2"/>
+      <c r="E350" s="2"/>
+    </row>
+    <row r="351" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C351" s="2"/>
+      <c r="D351" s="2"/>
+      <c r="E351" s="2"/>
+    </row>
+    <row r="356" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C356" s="2"/>
+      <c r="D356" s="2"/>
+      <c r="E356" s="2"/>
+    </row>
+    <row r="357" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C357" s="2"/>
+      <c r="D357" s="2"/>
+      <c r="E357" s="2"/>
+    </row>
+    <row r="364" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C364" s="2"/>
+      <c r="D364" s="2"/>
+      <c r="E364" s="2"/>
+    </row>
+    <row r="365" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C365" s="2"/>
+      <c r="D365" s="2"/>
+      <c r="E365" s="2"/>
+    </row>
+    <row r="370" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C370" s="2"/>
+      <c r="D370" s="2"/>
+      <c r="E370" s="2"/>
+    </row>
+    <row r="371" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C371" s="2"/>
+      <c r="D371" s="2"/>
+      <c r="E371" s="2"/>
+    </row>
+    <row r="378" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C378" s="2"/>
+      <c r="D378" s="2"/>
+      <c r="E378" s="2"/>
+    </row>
+    <row r="379" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C379" s="2"/>
+      <c r="D379" s="2"/>
+      <c r="E379" s="2"/>
+    </row>
+    <row r="384" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C384" s="2"/>
+      <c r="D384" s="2"/>
+      <c r="E384" s="2"/>
+    </row>
+    <row r="385" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C385" s="2"/>
+      <c r="D385" s="2"/>
+      <c r="E385" s="2"/>
+    </row>
+    <row r="392" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C392" s="2"/>
+      <c r="D392" s="2"/>
+      <c r="E392" s="2"/>
+    </row>
+    <row r="393" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C393" s="2"/>
+      <c r="D393" s="2"/>
+      <c r="E393" s="2"/>
+    </row>
+    <row r="398" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C398" s="2"/>
+      <c r="D398" s="2"/>
+      <c r="E398" s="2"/>
+    </row>
+    <row r="399" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C399" s="2"/>
+      <c r="D399" s="2"/>
+      <c r="E399" s="2"/>
+    </row>
+    <row r="406" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C406" s="2"/>
+      <c r="D406" s="2"/>
+      <c r="E406" s="2"/>
+    </row>
+    <row r="407" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C407" s="2"/>
+      <c r="D407" s="2"/>
+      <c r="E407" s="2"/>
+    </row>
+    <row r="420" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C420" s="2"/>
+      <c r="D420" s="2"/>
+      <c r="E420" s="2"/>
+    </row>
+    <row r="421" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C421" s="2"/>
+      <c r="D421" s="2"/>
+      <c r="E421" s="2"/>
+    </row>
+    <row r="434" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C434" s="2"/>
+      <c r="D434" s="2"/>
+      <c r="E434" s="2"/>
+    </row>
+    <row r="435" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C435" s="2"/>
+      <c r="D435" s="2"/>
+      <c r="E435" s="2"/>
+    </row>
+    <row r="448" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C448" s="2"/>
+      <c r="D448" s="2"/>
+      <c r="E448" s="2"/>
+    </row>
+    <row r="449" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C449" s="2"/>
+      <c r="D449" s="2"/>
+      <c r="E449" s="2"/>
+    </row>
+    <row r="462" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C462" s="2"/>
+      <c r="D462" s="2"/>
+      <c r="E462" s="2"/>
+    </row>
+    <row r="463" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C463" s="2"/>
+      <c r="D463" s="2"/>
+      <c r="E463" s="2"/>
+    </row>
+    <row r="476" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C476" s="2"/>
+      <c r="D476" s="2"/>
+      <c r="E476" s="2"/>
+    </row>
+    <row r="477" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C477" s="2"/>
+      <c r="D477" s="2"/>
+      <c r="E477" s="2"/>
+    </row>
+    <row r="490" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C490" s="2"/>
+      <c r="D490" s="2"/>
+      <c r="E490" s="2"/>
+    </row>
+    <row r="491" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C491" s="2"/>
+      <c r="D491" s="2"/>
+      <c r="E491" s="2"/>
+    </row>
+    <row r="500" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C500" s="2"/>
+      <c r="D500" s="2"/>
+      <c r="E500" s="2"/>
+    </row>
+    <row r="501" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C501" s="2"/>
+      <c r="D501" s="2"/>
+      <c r="E501" s="2"/>
+    </row>
+    <row r="502" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C502" s="2"/>
+      <c r="D502" s="2"/>
+      <c r="E502" s="2"/>
+    </row>
+    <row r="503" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C503" s="2"/>
+      <c r="D503" s="2"/>
+      <c r="E503" s="2"/>
+    </row>
+    <row r="504" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C504" s="2"/>
+      <c r="D504" s="2"/>
+      <c r="E504" s="2"/>
+    </row>
+    <row r="505" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C505" s="2"/>
+      <c r="D505" s="2"/>
+      <c r="E505" s="2"/>
+    </row>
+    <row r="514" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C514" s="2"/>
+      <c r="D514" s="2"/>
+      <c r="E514" s="2"/>
+    </row>
+    <row r="515" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C515" s="2"/>
+      <c r="D515" s="2"/>
+      <c r="E515" s="2"/>
+    </row>
+    <row r="516" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C516" s="2"/>
+      <c r="D516" s="2"/>
+      <c r="E516" s="2"/>
+    </row>
+    <row r="517" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C517" s="2"/>
+      <c r="D517" s="2"/>
+      <c r="E517" s="2"/>
+    </row>
+    <row r="518" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C518" s="2"/>
+      <c r="D518" s="2"/>
+      <c r="E518" s="2"/>
+    </row>
+    <row r="519" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C519" s="2"/>
+      <c r="D519" s="2"/>
+      <c r="E519" s="2"/>
+    </row>
+    <row r="528" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C528" s="2"/>
+      <c r="D528" s="2"/>
+      <c r="E528" s="2"/>
+    </row>
+    <row r="529" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C529" s="2"/>
+      <c r="D529" s="2"/>
+      <c r="E529" s="2"/>
+    </row>
+    <row r="530" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C530" s="2"/>
+      <c r="D530" s="2"/>
+      <c r="E530" s="2"/>
+    </row>
+    <row r="531" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C531" s="2"/>
+      <c r="D531" s="2"/>
+      <c r="E531" s="2"/>
+    </row>
+    <row r="532" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C532" s="2"/>
+      <c r="D532" s="2"/>
+      <c r="E532" s="2"/>
+    </row>
+    <row r="533" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C533" s="2"/>
+      <c r="D533" s="2"/>
+      <c r="E533" s="2"/>
+    </row>
+    <row r="542" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C542" s="2"/>
+      <c r="D542" s="2"/>
+      <c r="E542" s="2"/>
+    </row>
+    <row r="543" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C543" s="2"/>
+      <c r="D543" s="2"/>
+      <c r="E543" s="2"/>
+    </row>
+    <row r="544" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C544" s="2"/>
+      <c r="D544" s="2"/>
+      <c r="E544" s="2"/>
+    </row>
+    <row r="545" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C545" s="2"/>
+      <c r="D545" s="2"/>
+      <c r="E545" s="2"/>
+    </row>
+    <row r="546" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C546" s="2"/>
+      <c r="D546" s="2"/>
+      <c r="E546" s="2"/>
+    </row>
+    <row r="547" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C547" s="2"/>
+      <c r="D547" s="2"/>
+      <c r="E547" s="2"/>
+    </row>
+    <row r="548" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C548" s="2"/>
+      <c r="D548" s="2"/>
+      <c r="E548" s="2"/>
+    </row>
+    <row r="549" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C549" s="2"/>
+      <c r="D549" s="2"/>
+      <c r="E549" s="2"/>
+    </row>
+    <row r="558" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C558" s="2"/>
+      <c r="D558" s="2"/>
+      <c r="E558" s="2"/>
+    </row>
+    <row r="559" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C559" s="2"/>
+      <c r="D559" s="2"/>
+      <c r="E559" s="2"/>
+    </row>
+    <row r="562" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C562" s="2"/>
+      <c r="D562" s="2"/>
+      <c r="E562" s="2"/>
+    </row>
+    <row r="563" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C563" s="2"/>
+      <c r="D563" s="2"/>
+      <c r="E563" s="2"/>
+    </row>
+    <row r="572" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C572" s="2"/>
+      <c r="D572" s="2"/>
+      <c r="E572" s="2"/>
+    </row>
+    <row r="573" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C573" s="2"/>
+      <c r="D573" s="2"/>
+      <c r="E573" s="2"/>
+    </row>
+    <row r="576" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C576" s="2"/>
+      <c r="D576" s="2"/>
+      <c r="E576" s="2"/>
+    </row>
+    <row r="577" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C577" s="2"/>
+      <c r="D577" s="2"/>
+      <c r="E577" s="2"/>
+    </row>
+    <row r="586" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C586" s="2"/>
+      <c r="D586" s="2"/>
+      <c r="E586" s="2"/>
+    </row>
+    <row r="587" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C587" s="2"/>
+      <c r="D587" s="2"/>
+      <c r="E587" s="2"/>
+    </row>
+    <row r="590" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C590" s="2"/>
+      <c r="D590" s="2"/>
+      <c r="E590" s="2"/>
+    </row>
+    <row r="591" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C591" s="2"/>
+      <c r="D591" s="2"/>
+      <c r="E591" s="2"/>
+    </row>
+    <row r="600" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C600" s="2"/>
+      <c r="D600" s="2"/>
+      <c r="E600" s="2"/>
+    </row>
+    <row r="601" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C601" s="2"/>
+      <c r="D601" s="2"/>
+      <c r="E601" s="2"/>
+    </row>
+    <row r="604" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C604" s="2"/>
+      <c r="D604" s="2"/>
+      <c r="E604" s="2"/>
+    </row>
+    <row r="605" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C605" s="2"/>
+      <c r="D605" s="2"/>
+      <c r="E605" s="2"/>
+    </row>
+    <row r="614" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C614" s="2"/>
+      <c r="D614" s="2"/>
+      <c r="E614" s="2"/>
+    </row>
+    <row r="615" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C615" s="2"/>
+      <c r="D615" s="2"/>
+      <c r="E615" s="2"/>
+    </row>
+    <row r="618" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C618" s="2"/>
+      <c r="D618" s="2"/>
+      <c r="E618" s="2"/>
+    </row>
+    <row r="619" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C619" s="2"/>
+      <c r="D619" s="2"/>
+      <c r="E619" s="2"/>
+    </row>
+    <row r="632" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C632" s="2"/>
+      <c r="D632" s="2"/>
+      <c r="E632" s="2"/>
+    </row>
+    <row r="633" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C633" s="2"/>
+      <c r="D633" s="2"/>
+      <c r="E633" s="2"/>
+    </row>
+    <row r="646" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C646" s="2"/>
+      <c r="D646" s="2"/>
+      <c r="E646" s="2"/>
+    </row>
+    <row r="647" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C647" s="2"/>
+      <c r="D647" s="2"/>
+      <c r="E647" s="2"/>
+    </row>
+    <row r="660" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C660" s="2"/>
+      <c r="D660" s="2"/>
+      <c r="E660" s="2"/>
+    </row>
+    <row r="661" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C661" s="2"/>
+      <c r="D661" s="2"/>
+      <c r="E661" s="2"/>
+    </row>
+    <row r="674" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C674" s="2"/>
+      <c r="D674" s="2"/>
+      <c r="E674" s="2"/>
+    </row>
+    <row r="675" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C675" s="2"/>
+      <c r="D675" s="2"/>
+      <c r="E675" s="2"/>
+    </row>
+    <row r="690" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C690" s="2"/>
+      <c r="D690" s="2"/>
+      <c r="E690" s="2"/>
+    </row>
+    <row r="691" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C691" s="2"/>
+      <c r="D691" s="2"/>
+      <c r="E691" s="2"/>
+    </row>
+    <row r="692" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C692" s="2"/>
+      <c r="D692" s="2"/>
+      <c r="E692" s="2"/>
+    </row>
+    <row r="693" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C693" s="2"/>
+      <c r="D693" s="2"/>
+      <c r="E693" s="2"/>
+    </row>
+    <row r="698" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C698" s="2"/>
+      <c r="D698" s="2"/>
+      <c r="E698" s="2"/>
+    </row>
+    <row r="699" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C699" s="2"/>
+      <c r="D699" s="2"/>
+      <c r="E699" s="2"/>
+    </row>
+    <row r="700" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C700" s="2"/>
+      <c r="D700" s="2"/>
+      <c r="E700" s="2"/>
+    </row>
+    <row r="701" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C701" s="2"/>
+      <c r="D701" s="2"/>
+      <c r="E701" s="2"/>
+    </row>
+    <row r="704" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C704" s="2"/>
+      <c r="D704" s="2"/>
+      <c r="E704" s="2"/>
+    </row>
+    <row r="705" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C705" s="2"/>
+      <c r="D705" s="2"/>
+      <c r="E705" s="2"/>
+    </row>
+    <row r="708" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C708" s="2"/>
+      <c r="D708" s="2"/>
+      <c r="E708" s="2"/>
+    </row>
+    <row r="709" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C709" s="2"/>
+      <c r="D709" s="2"/>
+      <c r="E709" s="2"/>
+    </row>
+    <row r="712" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C712" s="2"/>
+      <c r="D712" s="2"/>
+      <c r="E712" s="2"/>
+    </row>
+    <row r="713" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C713" s="2"/>
+      <c r="D713" s="2"/>
+      <c r="E713" s="2"/>
+    </row>
+    <row r="716" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C716" s="2"/>
+      <c r="D716" s="2"/>
+      <c r="E716" s="2"/>
+    </row>
+    <row r="717" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C717" s="2"/>
+      <c r="D717" s="2"/>
+      <c r="E717" s="2"/>
+    </row>
+    <row r="728" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C728" s="2"/>
+      <c r="D728" s="2"/>
+      <c r="E728" s="2"/>
+    </row>
+    <row r="729" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C729" s="2"/>
+      <c r="D729" s="2"/>
+      <c r="E729" s="2"/>
+    </row>
+    <row r="736" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C736" s="2"/>
+      <c r="D736" s="2"/>
+      <c r="E736" s="2"/>
+    </row>
+    <row r="737" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C737" s="2"/>
+      <c r="D737" s="2"/>
+      <c r="E737" s="2"/>
+    </row>
+    <row r="738" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C738" s="2"/>
+      <c r="D738" s="2"/>
+      <c r="E738" s="2"/>
+    </row>
+    <row r="739" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C739" s="2"/>
+      <c r="D739" s="2"/>
+      <c r="E739" s="2"/>
+    </row>
+    <row r="742" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C742" s="2"/>
+      <c r="D742" s="2"/>
+      <c r="E742" s="2"/>
+    </row>
+    <row r="743" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C743" s="2"/>
+      <c r="D743" s="2"/>
+      <c r="E743" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fd82ce5f74cc55317d54acf2fd8d0884">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1c7e28f2e213f6984c438ed744cd3c36" ns2:_="" ns3:_="">
+    <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
+    <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="18" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="f8ebb0a5-c57d-4c3a-bec7-8a38252dd05c" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="fb9e4d32-074f-4c04-81ef-e811753dfd59" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="16" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="17" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{d5300f42-37b4-4000-b69c-e0298172bf57}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="fb9e4d32-074f-4c04-81ef-e811753dfd59">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B37C24B4-649E-42AB-A039-509573449337}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
+    <ds:schemaRef ds:uri="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A194708A-8AFE-469B-8989-87632D25BD46}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
+    <ds:schemaRef ds:uri="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{829B573D-FB72-4DC1-BC88-BDE6C499175D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>